--- a/Design Files/Main Board - v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
+++ b/Design Files/Main Board - v1.0/BOM/Client-BOM-Main Board - v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="124">
   <si>
     <t>#</t>
   </si>
@@ -153,9 +153,6 @@
     <t>85dB Passive (external drive) Electromagnetic Type 2kHz Plugin,D=12mm Buzzers ROHS</t>
   </si>
   <si>
-    <t>I2C OLED Display 0.96 Inch IIC Serial LCD LED Module SSD1306 128 64 for Arduino with 40 Pcs Dupont Wire</t>
-  </si>
-  <si>
     <t>TRANS NPN 40V 0.6A SMD SOT23-3</t>
   </si>
   <si>
@@ -171,18 +168,12 @@
     <t>RES SMD 1K OHM 1% 1/5W 0402</t>
   </si>
   <si>
-    <t>RES 2K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
     <t>RES 470 OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 100 OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>ESP32-C3-MINI-1 DEV BRD</t>
-  </si>
-  <si>
     <t>IC BATT CNTL LI-ION 1CEL SOT23-5</t>
   </si>
   <si>
@@ -219,18 +210,12 @@
     <t>Res-0402</t>
   </si>
   <si>
-    <t>ESP32-C3-DEVKITM-1</t>
-  </si>
-  <si>
     <t>SOT-23-5</t>
   </si>
   <si>
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>C1005X5R1H104K050BB</t>
-  </si>
-  <si>
     <t>CL10A106MA8NRNC</t>
   </si>
   <si>
@@ -261,9 +246,6 @@
     <t>CRCW04021K00FKEDHP</t>
   </si>
   <si>
-    <t>RC0402FR-072KL</t>
-  </si>
-  <si>
     <t>RC0402FR-07470RL</t>
   </si>
   <si>
@@ -342,9 +324,6 @@
     <t>1K</t>
   </si>
   <si>
-    <t>2K</t>
-  </si>
-  <si>
     <t>470R</t>
   </si>
   <si>
@@ -387,7 +366,31 @@
     <t>701535 3.7V 350mAh Polymer Lithium Rechargeable Battery for Bluetooth Headset Dog Training Device Credit Card Machine Battery</t>
   </si>
   <si>
-    <t xml:space="preserve">OLED SSD1306 </t>
+    <t>1.3 inch I2C OLED Display 128x64 - Blue/Black</t>
+  </si>
+  <si>
+    <t>1.3 inch I2C OLED Display</t>
+  </si>
+  <si>
+    <t>Robolink</t>
+  </si>
+  <si>
+    <t>C1005X7R1H104KT000F</t>
+  </si>
+  <si>
+    <t>ESP32-PICO-KIT-1</t>
+  </si>
+  <si>
+    <t>Development Board ESP32-PICO-V3</t>
+  </si>
+  <si>
+    <t>RC0402FR-076K8L</t>
+  </si>
+  <si>
+    <t>6.8K</t>
+  </si>
+  <si>
+    <t>RES 6.8K OHM 1% 1/16W 0402</t>
   </si>
 </sst>
 </file>
@@ -599,9 +602,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -610,6 +610,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -923,9 +926,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -942,22 +945,22 @@
         <v>35</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -976,16 +979,16 @@
         <v>36</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J3" s="7">
         <v>2</v>
@@ -1008,16 +1011,16 @@
         <v>37</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J4" s="9">
         <v>4</v>
@@ -1031,7 +1034,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>17</v>
@@ -1040,16 +1043,16 @@
         <v>38</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -1072,16 +1075,16 @@
         <v>39</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
@@ -1104,16 +1107,16 @@
         <v>40</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -1136,16 +1139,16 @@
         <v>41</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -1168,16 +1171,16 @@
         <v>42</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>114</v>
+        <v>86</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>107</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -1200,23 +1203,23 @@
         <v>43</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -1229,25 +1232,25 @@
         <v>23</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J11" s="7">
         <v>1</v>
       </c>
-      <c r="K11" s="17" t="s">
-        <v>120</v>
+      <c r="K11" s="16" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1263,19 +1266,19 @@
         <v>24</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -1295,19 +1298,19 @@
         <v>25</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J13" s="7">
         <v>1</v>
@@ -1327,19 +1330,19 @@
         <v>26</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="J14" s="9">
         <v>4</v>
@@ -1359,19 +1362,19 @@
         <v>27</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
@@ -1391,19 +1394,19 @@
         <v>28</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1423,19 +1426,19 @@
         <v>29</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -1455,19 +1458,19 @@
         <v>30</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -1487,19 +1490,19 @@
         <v>31</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -1519,19 +1522,19 @@
         <v>32</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -1551,19 +1554,19 @@
         <v>33</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -1583,19 +1586,19 @@
         <v>34</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J22" s="9">
         <v>1</v>
@@ -1608,31 +1611,31 @@
         <v>21</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F23" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" s="9">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="9">
-        <v>1</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
